--- a/diseases/d200/2005-2009.xlsx
+++ b/diseases/d200/2005-2009.xlsx
@@ -1009,7 +1009,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1415,7 +1415,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1821,7 +1821,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2227,7 +2227,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2633,7 +2633,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -3039,7 +3039,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3445,7 +3445,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3851,7 +3851,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4257,7 +4257,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4663,7 +4663,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -5069,7 +5069,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5475,7 +5475,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
